--- a/WEB/public/template_user.xlsx
+++ b/WEB/public/template_user.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\Jtisphere\WEB\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Music\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A15B15E4-B208-431C-A646-E11FAFBCE7E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B1E4E093-24A3-44FE-9DCD-ED0CB91C5C92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{5C25F105-3A2A-435A-BF2F-E1B18E004B59}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>username</t>
   </si>
@@ -40,13 +40,19 @@
   </si>
   <si>
     <t>level_id</t>
+  </si>
+  <si>
+    <t>Rawansyah, Drs., M.Pd</t>
+  </si>
+  <si>
+    <t>Rawansyah</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -58,6 +64,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF262626"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -83,9 +96,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -400,7 +416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{108191CB-6260-4EB6-8BD7-DF5F236E6406}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="18.28515625" customWidth="1"/>
@@ -426,6 +442,23 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2">
+        <v>12345</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="4">
+        <v>1.9590620199403101E+17</v>
+      </c>
+      <c r="E2" s="2">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
